--- a/VerveStacks_ARE_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ARE_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF81FAF6-FA1D-4F6E-8699-6CAB1272E50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2627B61-2F20-493F-938C-CAA46ACF5E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0D07BCED-C83E-4A4F-8654-0A2D9944A6E3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F2AEC59-35C4-4D40-93F2-1F3C57606487}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1675,7 +1675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7671FF-7CAE-4531-B130-5534B9897089}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6DA7E77-36A2-435D-A7BB-22079E3D9E61}">
   <dimension ref="B3:L178"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ARE_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2627B61-2F20-493F-938C-CAA46ACF5E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F119E0-6184-4E88-BDED-D372A172C07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F2AEC59-35C4-4D40-93F2-1F3C57606487}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AAFD68BE-48B3-4A0E-9A25-8C68B2AAA0BA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1675,7 +1675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6DA7E77-36A2-435D-A7BB-22079E3D9E61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0088C20-54E3-48B0-8012-EA5303665C38}">
   <dimension ref="B3:L178"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_ARE_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F119E0-6184-4E88-BDED-D372A172C07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EBAAC9E-FB14-4653-A62E-12D14248F168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AAFD68BE-48B3-4A0E-9A25-8C68B2AAA0BA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{99144F36-F443-443A-B895-FEEB7BDE93E2}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1675,7 +1675,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0088C20-54E3-48B0-8012-EA5303665C38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF99E02-E558-4119-ACD9-84711C06EB65}">
   <dimension ref="B3:L178"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
